--- a/internet_speed_test/internet_speed_log.xlsx
+++ b/internet_speed_test/internet_speed_log.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedTestLog" displayName="SpeedTestLog" ref="A1:O30" headerRowCount="1">
-  <autoFilter ref="A1:O30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedTestLog" displayName="SpeedTestLog" ref="A1:O31" headerRowCount="1">
+  <autoFilter ref="A1:O31"/>
   <tableColumns count="15">
     <tableColumn id="1" name="timestamp"/>
     <tableColumn id="2" name="server"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -537,12 +537,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21 21:07:59</t>
+          <t>2026-07-27 22:34:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nairobi, Nairobi County, KE</t>
+          <t>Kisii, Kisii County, KE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -567,51 +567,51 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.28333</t>
+          <t>-0.68174</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36.81667</t>
+          <t>34.76666</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
+          <t>For Safaricom KENYA Enterprise Business Unit</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>105.161.229.201</t>
+          <t>197.248.135.5</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.98</v>
+        <v>4.44</v>
       </c>
       <c r="L2" t="n">
-        <v>1.98</v>
+        <v>4.51</v>
       </c>
       <c r="M2" t="n">
-        <v>279.01</v>
+        <v>130.45</v>
       </c>
       <c r="N2" t="n">
-        <v>147.51</v>
+        <v>592.3099999999999</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>night with slow connection in Nandi Hills, Safaricom 5g again, super slow, going to restart connection</t>
+          <t>bad wifi, using my Alex wifi in Kesses</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21 20:56:50</t>
+          <t>2026-06-21 21:07:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -656,39 +656,39 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>337.83</t>
+          <t>279.01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>925.06</t>
+          <t>147.51</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>night with slow connection in Nandi Hills, Safaricom 5g</t>
+          <t>night with slow connection in Nandi Hills, Safaricom 5g again, super slow, going to restart connection</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-15 13:11:24</t>
+          <t>2026-06-21 20:56:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -723,44 +723,44 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>For Safaricom KENYA Enterprise Business Unit</t>
+          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>197.248.135.5</t>
+          <t>105.161.229.201</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>118.96</t>
+          <t>337.83</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>925.06</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>without using cloudflare vpn, on ethernet, in kesses</t>
+          <t>night with slow connection in Nandi Hills, Safaricom 5g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-15 12:32:47</t>
+          <t>2026-06-15 13:11:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Eldoret, Uasin Gishu County, KE</t>
+          <t>Nairobi, Nairobi County, KE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.52036</t>
+          <t>-1.28333</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>35.26993</t>
+          <t>36.81667</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -810,39 +810,39 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>27.11</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>151.55</t>
+          <t>118.96</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>370.62</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>molly complained about royuter named "Mike" in kesses</t>
+          <t>without using cloudflare vpn, on ethernet, in kesses</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-14 18:52:53</t>
+          <t>2026-06-15 12:32:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -852,74 +852,74 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Benoni, Gauteng, ZA</t>
+          <t>Eldoret, Uasin Gishu County, KE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-26.18848</t>
+          <t>0.52036</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.32078</t>
+          <t>35.26993</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cloudflare London, LLC</t>
+          <t>For Safaricom KENYA Enterprise Business Unit</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2a09:bac5:d4f7:2e64::49f:1f</t>
+          <t>197.248.135.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>296.93</t>
+          <t>151.55</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>370.62</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>at night in kessess on router</t>
+          <t>molly complained about royuter named "Mike" in kesses</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12 20:44:35</t>
+          <t>2026-06-14 18:52:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DUR</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -929,69 +929,69 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Eldoret, Uasin Gishu County, KE</t>
+          <t>Benoni, Gauteng, ZA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.52036</t>
+          <t>-26.18848</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35.26993</t>
+          <t>28.32078</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>For Safaricom KENYA Enterprise Business Unit</t>
+          <t>Cloudflare London, LLC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>197.248.135.5</t>
+          <t>2a09:bac5:d4f7:2e64::49f:1f</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>152.31</t>
+          <t>296.93</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>444.48</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>very jerky  internet in kesses tonight</t>
+          <t>at night in kessess on router</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12 18:18:43</t>
+          <t>2026-06-12 20:44:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N/A, N/A, KE</t>
+          <t>Eldoret, Uasin Gishu County, KE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.52036</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.26993</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>For Safaricom KENYA Enterprise Business Unit</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1041,39 +1041,39 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>159.04</t>
+          <t>152.31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>567.35</t>
+          <t>444.48</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>very bad lintermittent internet in kesses</t>
+          <t>very jerky  internet in kesses tonight</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-07 21:46:34</t>
+          <t>2026-06-12 18:18:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>DUR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1083,252 +1083,248 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Frankfurt am Main, Hesse, DE</t>
+          <t>N/A, N/A, KE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50.11552</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.68417</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Packethub S.A.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>212.97.68.40</t>
+          <t>197.248.135.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>788.13</t>
+          <t>159.04</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>567.35</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>chnaged  nord vpn protocol to nordlynx (wireguard) in kesses</t>
+          <t>very bad lintermittent internet in kesses</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>2026-06-07 21:46:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>server</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sponsor</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Frankfurt am Main, Hesse, DE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>50.11552</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>lon</t>
+          <t>8.68417</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>isp</t>
+          <t>Packethub S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>212.97.68.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>download_mbps</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>upload_mbps</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ping_ms</t>
+          <t>788.13</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>jitter_ms</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Column1</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Column2</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Column3</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Column4</t>
+          <t>chnaged  nord vpn protocol to nordlynx (wireguard) in kesses</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6/7/2026 21:19</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dallas, Texas, US</t>
+          <t>location</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>country</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.78306</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-96.80667</t>
+          <t>lon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Packethub S.A.</t>
+          <t>isp</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>185.255.130.240</t>
+          <t>ip</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>download_mbps</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>upload_mbps</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>928.62</t>
+          <t>ping_ms</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>124.06</t>
+          <t>jitter_ms</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>nordvpn connection to dallas USA</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Column1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Column2</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Column3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Column4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6/7/2026 18:50</t>
+          <t>6/7/2026 21:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JNB</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,62 +1334,62 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Benoni, Gauteng, ZA</t>
+          <t>Dallas, Texas, US</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-26.18848</t>
+          <t>32.78306</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28.32078</t>
+          <t>-96.80667</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cloudflare London, LLC</t>
+          <t>Packethub S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2a09:bac5:d4f4:2e64::49f:4d</t>
+          <t>185.255.130.240</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>320.02</t>
+          <t>928.62</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>57.65</t>
+          <t>124.06</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>using  cloudflares VPN "warp" in kesses</t>
+          <t>nordvpn connection to dallas USA</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1404,12 +1400,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6/6/2026 15:11</t>
+          <t>6/7/2026 18:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>JNB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1419,62 +1415,62 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nairobi, Nairobi County, KE</t>
+          <t>Benoni, Gauteng, ZA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.28333</t>
+          <t>-26.18848</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>36.81667</t>
+          <t>28.32078</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
+          <t>Cloudflare London, LLC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>105.160.48.114</t>
+          <t>2a09:bac5:d4f4:2e64::49f:4d</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>272.03</t>
+          <t>320.02</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>756.79</t>
+          <t>57.65</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>at  Samara and slamas place</t>
+          <t>using  cloudflares VPN "warp" in kesses</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1485,12 +1481,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6/6/2026 10:54</t>
+          <t>6/6/2026 15:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1500,7 +1496,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Eldoret, Uasin Gishu County, KE</t>
+          <t>Nairobi, Nairobi County, KE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1515,47 +1511,47 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.52036</t>
+          <t>-1.28333</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.26993</t>
+          <t>36.81667</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>For Converged services in Eastern Region</t>
+          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41.139.184.9</t>
+          <t>105.160.48.114</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>114.68</t>
+          <t>272.03</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>108.59</t>
+          <t>756.79</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EKA Hotel Wifi</t>
+          <t>at  Samara and slamas place</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1634,7 +1630,11 @@
           <t>108.59</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>EKA Hotel Wifi</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1643,12 +1643,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6/3/2026 23:01</t>
+          <t>6/6/2026 10:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nairobi, Nairobi County, KE</t>
+          <t>Eldoret, Uasin Gishu County, KE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1673,49 +1673,45 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.28333</t>
+          <t>0.52036</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>36.81667</t>
+          <t>35.26993</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SpaceX Services, Inc.</t>
+          <t>For Converged services in Eastern Region</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>129.222.147.209</t>
+          <t>41.139.184.9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>148.42</t>
+          <t>114.68</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3695.88</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>early mornign tesst, in kesses</t>
-        </is>
-      </c>
+          <t>108.59</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1724,12 +1720,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6/3/2026 15:22</t>
+          <t>6/3/2026 23:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1764,37 +1760,37 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>For Safaricom KENYA Enterprise Business Unit</t>
+          <t>SpaceX Services, Inc.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>197.248.135.5</t>
+          <t>129.222.147.209</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>16.12</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>117.25</t>
+          <t>148.42</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>375.81</t>
+          <t>3695.88</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>after paying my neternet bill in kesses</t>
+          <t>early mornign tesst, in kesses</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1873,7 +1869,11 @@
           <t>375.81</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>after paying my neternet bill in kesses</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1882,12 +1882,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5/31/2026 14:16</t>
+          <t>6/3/2026 15:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NBO</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1922,39 +1922,35 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
+          <t>For Safaricom KENYA Enterprise Business Unit</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>105.161.158.119</t>
+          <t>197.248.135.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>199.86</t>
+          <t>117.25</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>40.9</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>after storm in nandi hill on sheilas wifi</t>
-        </is>
-      </c>
+          <t>375.81</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1963,12 +1959,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5/27/2026 20:09</t>
+          <t>5/31/2026 14:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MRS</t>
+          <t>NBO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2003,37 +1999,37 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SAFARICOM PUBLIC POOL A</t>
+          <t>KE-SFC-GPRS-EDGE-3G-LTE-Mobile WiFi-SERVICE-IP</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>196.96.39.233</t>
+          <t>105.161.158.119</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>181.26</t>
+          <t>199.86</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>334.36</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sheilas router in Nandi Hills, safaricom 5G</t>
+          <t>after storm in nandi hill on sheilas wifi</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2044,7 +2040,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5/21/2026 19:37</t>
+          <t>5/27/2026 20:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2089,32 +2085,32 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>196.96.33.138</t>
+          <t>196.96.39.233</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>210.44</t>
+          <t>181.26</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>334.36</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>On my phones hotspot, in nandi hills</t>
+          <t>Sheilas router in Nandi Hills, safaricom 5G</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2125,77 +2121,77 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2/4/2026 3:07</t>
+          <t>5/21/2026 19:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humble, TX</t>
+          <t>MRS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tachus Fiber Internet</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Humble, TX, United States</t>
+          <t>Nairobi, Nairobi County, KE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.9988</t>
+          <t>-1.28333</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-95.2622</t>
+          <t>36.81667</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Clouvider Limited</t>
+          <t>SAFARICOM PUBLIC POOL A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.56.191.106</t>
+          <t>196.96.33.138</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>302.53</t>
+          <t>210.44</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1020.24</t>
+          <t>57.93</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>connected to US -Dallas Nord VPN</t>
+          <t>On my phones hotspot, in nandi hills</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2206,77 +2202,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2/4/2026 1:16</t>
+          <t>2/4/2026 3:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Humble, TX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AfriQ Networks Kenya</t>
+          <t>Tachus Fiber Internet</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>Humble, TX, United States</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.2833</t>
+          <t>29.9988</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>36.8167</t>
+          <t>-95.2622</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Safaricom Business</t>
+          <t>Clouvider Limited</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>41.139.243.39</t>
+          <t>2.56.191.106</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>302.53</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>1020.24</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>took long, check latency and jitter</t>
+          <t>connected to US -Dallas Nord VPN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2287,7 +2283,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2/3/2026 23:43</t>
+          <t>2/4/2026 1:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2297,7 +2293,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unwired Communications</t>
+          <t>AfriQ Networks Kenya</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2337,27 +2333,27 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Looks good so far!</t>
+          <t>took long, check latency and jitter</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2368,7 +2364,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2/3/2026 18:10</t>
+          <t>2/3/2026 23:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2378,7 +2374,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AfriQ Networks Kenya</t>
+          <t>Unwired Communications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2418,27 +2414,27 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>again without vpn</t>
+          <t>Looks good so far!</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2449,7 +2445,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2/3/2026 17:57</t>
+          <t>2/3/2026 18:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2499,27 +2495,27 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>without VPN</t>
+          <t>again without vpn</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2530,7 +2526,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2/3/2026 16:14</t>
+          <t>2/3/2026 17:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2540,7 +2536,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zuku</t>
+          <t>AfriQ Networks Kenya</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2580,27 +2576,27 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>28.83</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>test 3, have not reset adapter after  turning off vpn</t>
+          <t>without VPN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2681,7 +2677,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>test 3</t>
+          <t>test 3, have not reset adapter after  turning off vpn</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2692,7 +2688,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2/3/2026 15:50</t>
+          <t>2/3/2026 16:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2702,7 +2698,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PepeaNet</t>
+          <t>Zuku</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2742,27 +2738,27 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>writting another comment to test if recorded in log</t>
+          <t>test 3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2841,11 +2837,92 @@
           <t>0</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>writting another comment to test if recorded in log</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2/3/2026 15:50</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PepeaNet</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nairobi, Kenya</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-1.2833</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>36.8167</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Safaricom Business</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>41.139.243.39</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>26.05</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>44.32</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
